--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484590_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484590_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.7828</v>
+        <v>9.2036</v>
       </c>
       <c r="E2" t="n">
-        <v>6.636</v>
+        <v>6.8834</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1468</v>
+        <v>2.3202</v>
       </c>
       <c r="G2" t="n">
         <v>6.8143</v>
@@ -610,13 +610,13 @@
         <v>3.8484</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3142</v>
+        <v>-0.8935</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.3228</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7441</v>
+        <v>-0.5707</v>
       </c>
       <c r="V2" t="n">
         <v>1.267</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5456</v>
+        <v>4.9109</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2995</v>
+        <v>3.7392</v>
       </c>
       <c r="F3" t="n">
-        <v>1.246</v>
+        <v>1.1717</v>
       </c>
       <c r="G3" t="n">
         <v>4.4396</v>
@@ -688,13 +688,13 @@
         <v>2.3823</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3497</v>
+        <v>-0.9844000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7157</v>
+        <v>-0.276</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.634</v>
+        <v>-0.7084</v>
       </c>
       <c r="V3" t="n">
         <v>-0.0104</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7069</v>
+        <v>2.6622</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7998</v>
+        <v>1.1267</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9071</v>
+        <v>1.5355</v>
       </c>
       <c r="G4" t="n">
         <v>1.0767</v>
@@ -766,13 +766,13 @@
         <v>1.8326</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2741</v>
+        <v>0.2294</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0423</v>
+        <v>0.3692</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2319</v>
+        <v>-0.1397</v>
       </c>
       <c r="V4" t="n">
         <v>0.6231</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPIÑA</t>
+          <t>H. FABREGAT LORES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2753</v>
+        <v>1.2994</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2753</v>
+        <v>1.2628</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.0366</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2753</v>
+        <v>3.4013</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6502</v>
+        <v>3.1321</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6251</v>
+        <v>0.2691</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2753</v>
+        <v>4.4305</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6502</v>
+        <v>3.0712</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6251</v>
+        <v>1.3593</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-1.0293</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.0609</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-1.0902</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.4819</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-1.246</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.4189</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.8270999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. FABREGAT LORES</t>
+          <t>L. RODRIGUEZ CAMPIÑA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9747</v>
+        <v>1.2753</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1116</v>
+        <v>1.2753</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1368</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3.4013</v>
+        <v>1.2753</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1321</v>
+        <v>0.6502</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2691</v>
+        <v>0.6251</v>
       </c>
       <c r="J6" t="n">
-        <v>4.4305</v>
+        <v>1.2753</v>
       </c>
       <c r="K6" t="n">
-        <v>3.0712</v>
+        <v>0.6502</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3593</v>
+        <v>0.6251</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0293</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0609</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0902</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.4819</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5707</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5701000000000001</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0005</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8125</v>
+        <v>0.9141</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4998</v>
+        <v>1.651</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6873</v>
+        <v>-0.7368</v>
       </c>
       <c r="G7" t="n">
         <v>0.1592</v>
@@ -1000,13 +1000,13 @@
         <v>2.3823</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4071</v>
+        <v>-1.3054</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6364</v>
+        <v>-0.6859</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3219</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. MUÑOZ TORREGROSA</t>
+          <t>A. MELGAR GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3251</v>
+        <v>0.4186</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3251</v>
+        <v>-0.1677</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.5863</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3251</v>
+        <v>1.7434</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3251</v>
+        <v>1.0095</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.7339</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3251</v>
+        <v>0.9362</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3251</v>
+        <v>0.8111</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.8072</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.1983</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.6089</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.0683</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.2968</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.365</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.2566</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MELGAR GARCIA</t>
+          <t>D. MUÑOZ TORREGROSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3224</v>
+        <v>0.3251</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2639</v>
+        <v>0.3251</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5863</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7434</v>
+        <v>0.3251</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0095</v>
+        <v>0.3251</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7339</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9362</v>
+        <v>0.3251</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8111</v>
+        <v>0.3251</v>
       </c>
       <c r="L9" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8072</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1983</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6089</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1644</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2006</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.365</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2566</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3011</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. CHOFRE TARREGA</t>
+          <t>J. ROIG MESA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1092</v>
+        <v>-0.0049</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9472</v>
+        <v>-0.7159</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8379</v>
+        <v>0.7109</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5132</v>
+        <v>0.254</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3016</v>
+        <v>0.6609</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2116</v>
+        <v>-0.4069</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1583</v>
+        <v>-0.5228</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3993</v>
+        <v>0.1084</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5577</v>
+        <v>-0.6312</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6715</v>
+        <v>0.7768</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0977</v>
+        <v>0.5525</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7692</v>
+        <v>0.2243</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5498</v>
+        <v>1.0995</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5498</v>
+        <v>1.0995</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2493</v>
+        <v>-0.7146</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3107</v>
+        <v>-0.1931</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0614</v>
+        <v>-0.5215</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3219</v>
+        <v>-0.6439</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3219</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. ROIG MESA</t>
+          <t>E. CHOFRE TARREGA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3459</v>
+        <v>-0.0102</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9082</v>
+        <v>-0.9472</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5623</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>0.254</v>
+        <v>0.5132</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6609</v>
+        <v>0.3016</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4069</v>
+        <v>0.2116</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5228</v>
+        <v>-0.1583</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1084</v>
+        <v>0.3993</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6312</v>
+        <v>-0.5577</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7768</v>
+        <v>0.6715</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5525</v>
+        <v>-0.0977</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2243</v>
+        <v>0.7692</v>
       </c>
       <c r="P11" t="n">
-        <v>1.0995</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0995</v>
+        <v>0.5498</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0555</v>
+        <v>0.3484</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3854</v>
+        <v>0.3107</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6701</v>
+        <v>0.0377</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6439</v>
+        <v>-0.3219</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6439</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4232</v>
+        <v>-0.3984</v>
       </c>
       <c r="E12" t="n">
         <v>-0.7511</v>
       </c>
       <c r="F12" t="n">
-        <v>0.328</v>
+        <v>0.3528</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5128</v>
@@ -1390,13 +1390,13 @@
         <v>0.1833</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0936</v>
+        <v>-0.0688</v>
       </c>
       <c r="T12" t="n">
         <v>-0.1101</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0165</v>
+        <v>0.0413</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPINA</t>
+          <t>D. HOYAS PEREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.4143</v>
+        <v>-2.2229</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.7713</v>
+        <v>-1.8338</v>
       </c>
       <c r="F13" t="n">
-        <v>0.357</v>
+        <v>-0.3891</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.2578</v>
+        <v>1.7098</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.1038</v>
+        <v>1.3636</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.154</v>
+        <v>0.3461</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.0299</v>
+        <v>0.8461</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.1648</v>
+        <v>0.8203</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1349</v>
+        <v>0.0258</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2279</v>
+        <v>0.8637</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0609</v>
+        <v>0.5433</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2888</v>
+        <v>0.3204</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.2828</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.8484</v>
+        <v>-2.9321</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5656</v>
+        <v>0.9163</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1263</v>
+        <v>-0.6499</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5181</v>
+        <v>-0.0697</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3918</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5889</v>
+        <v>0.3219</v>
       </c>
       <c r="X13" t="n">
         <v>-1.5889</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. HOYAS PEREZ</t>
+          <t>L. RODRIGUEZ CAMPINA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.7285</v>
+        <v>-3.1558</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.3146</v>
+        <v>-3.6366</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4139</v>
+        <v>0.4808</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7098</v>
+        <v>-2.2578</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3636</v>
+        <v>-2.1038</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3461</v>
+        <v>-0.154</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8461</v>
+        <v>-2.0299</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8203</v>
+        <v>-2.1648</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0258</v>
+        <v>0.1349</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8637</v>
+        <v>-0.2279</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5433</v>
+        <v>0.0609</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3204</v>
+        <v>-0.2888</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.0158</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9321</v>
+        <v>-3.8484</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9163</v>
+        <v>2.5656</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1554</v>
+        <v>0.3848</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5505</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6049</v>
+        <v>-0.2679</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3219</v>
+        <v>1.5889</v>
       </c>
       <c r="X14" t="n">
         <v>-1.5889</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.1024</v>
+        <v>-4.3198</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.6328</v>
+        <v>-5.5777</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5304</v>
+        <v>1.2579</v>
       </c>
       <c r="G15" t="n">
         <v>-4.5708</v>
@@ -1624,13 +1624,13 @@
         <v>3.4819</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8589</v>
+        <v>-1.0764</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5151</v>
+        <v>-0.46</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3438</v>
+        <v>-0.6163</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3219</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>10.6218</v>
+        <v>10.8972</v>
       </c>
       <c r="E16" t="n">
-        <v>2.357999999999999</v>
+        <v>2.633500000000002</v>
       </c>
       <c r="F16" t="n">
-        <v>8.263800000000002</v>
+        <v>8.2638</v>
       </c>
       <c r="G16" t="n">
         <v>14.37050000000001</v>
@@ -1672,7 +1672,7 @@
         <v>17.095</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.724899999999999</v>
+        <v>-2.7249</v>
       </c>
       <c r="J16" t="n">
         <v>14.8393</v>
@@ -1681,10 +1681,10 @@
         <v>15.1575</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3183000000000002</v>
+        <v>-0.3182999999999998</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4691000000000004</v>
+        <v>-0.4691000000000001</v>
       </c>
       <c r="N16" t="n">
         <v>1.9373</v>
@@ -1693,7 +1693,7 @@
         <v>-2.4065</v>
       </c>
       <c r="P16" t="n">
-        <v>6.413899999999998</v>
+        <v>6.4139</v>
       </c>
       <c r="Q16" t="n">
         <v>-17.4094</v>
@@ -1702,10 +1702,10 @@
         <v>23.8234</v>
       </c>
       <c r="S16" t="n">
-        <v>-6.319800000000001</v>
+        <v>-6.044700000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.116</v>
+        <v>-0.8407000000000002</v>
       </c>
       <c r="U16" t="n">
         <v>-5.2036</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2588</v>
+        <v>2.1646</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4096</v>
+        <v>1.7365</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8492</v>
+        <v>0.428</v>
       </c>
       <c r="G17" t="n">
         <v>-3.746</v>
@@ -1780,13 +1780,13 @@
         <v>2.5656</v>
       </c>
       <c r="S17" t="n">
-        <v>2.45</v>
+        <v>1.3558</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6825</v>
+        <v>1.0095</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7675</v>
+        <v>0.3463</v>
       </c>
       <c r="V17" t="n">
         <v>3.8217</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. CARRION BALLESTER</t>
+          <t>M. CISNEROS RUIZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4669</v>
+        <v>1.303</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4746</v>
+        <v>0.5613</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9414</v>
+        <v>0.7416</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7894</v>
+        <v>-0.0808</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7060999999999999</v>
+        <v>0.8071</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0833</v>
+        <v>-0.8879</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2976</v>
+        <v>0.53</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8296</v>
+        <v>0.5202</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5319</v>
+        <v>0.0098</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.087</v>
+        <v>-0.6109</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5356</v>
+        <v>0.2869</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4486</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="P18" t="n">
         <v>0.733</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5656</v>
+        <v>0.733</v>
       </c>
       <c r="S18" t="n">
-        <v>1.8452</v>
+        <v>0.0277</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0604</v>
+        <v>0.0313</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7848000000000001</v>
+        <v>-0.0036</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3219</v>
+        <v>0.6231</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3219</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9779</v>
+        <v>1.2227</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2079</v>
+        <v>1.3041</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.23</v>
+        <v>-0.0814</v>
       </c>
       <c r="G19" t="n">
         <v>0.9182</v>
@@ -1936,13 +1936,13 @@
         <v>1.6493</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1573</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1116</v>
+        <v>-0.0154</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0457</v>
+        <v>0.1029</v>
       </c>
       <c r="V19" t="n">
         <v>2.2328</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. CISNEROS RUIZ</t>
+          <t>D. OLID SANGUESA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.742</v>
+        <v>0.7953</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2729</v>
+        <v>0.1784</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4691</v>
+        <v>0.617</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0808</v>
+        <v>0.1679</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8071</v>
+        <v>-0.2167</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8879</v>
+        <v>0.3846</v>
       </c>
       <c r="J20" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5202</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0098</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6109</v>
+        <v>0.1679</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2869</v>
+        <v>-0.2167</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8977000000000001</v>
+        <v>0.3846</v>
       </c>
       <c r="P20" t="n">
-        <v>0.733</v>
+        <v>0.3665</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.733</v>
+        <v>0.3665</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5333</v>
+        <v>0.2609</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2572</v>
+        <v>0.1784</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2761</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. OLID SANGUESA</t>
+          <t>F. BLASCO MANZANO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4573</v>
+        <v>0.3006</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1101</v>
+        <v>0.2587</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5674</v>
+        <v>0.042</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1679</v>
+        <v>-0.1687</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2167</v>
+        <v>-3.2783</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3846</v>
+        <v>3.1097</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1.8342</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>-0.8269</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.6611</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1679</v>
+        <v>-2.0029</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2167</v>
+        <v>-2.4514</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3846</v>
+        <v>0.4486</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3665</v>
+        <v>-0.733</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3665</v>
+        <v>2.0158</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0771</v>
+        <v>0.5584</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1101</v>
+        <v>0.5294</v>
       </c>
       <c r="U21" t="n">
-        <v>0.033</v>
+        <v>0.029</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. CARRION BALLESTER</t>
+          <t>A. CARRION BALLESTER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0766</v>
+        <v>0.2765</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0367</v>
+        <v>-1.2438</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1133</v>
+        <v>1.5203</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9489</v>
+        <v>-0.7894</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.0167</v>
+        <v>-0.7060999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0678</v>
+        <v>-0.0833</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.735</v>
+        <v>0.2976</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.5208</v>
+        <v>0.8296</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7857</v>
+        <v>-0.5319</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2139</v>
+        <v>-1.087</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4959</v>
+        <v>-1.5356</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2821</v>
+        <v>0.4486</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.2828</v>
+        <v>0.733</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.6651</v>
+        <v>-1.8326</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3823</v>
+        <v>2.5656</v>
       </c>
       <c r="S22" t="n">
-        <v>1.7194</v>
+        <v>0.6548</v>
       </c>
       <c r="T22" t="n">
-        <v>1.7745</v>
+        <v>0.2911</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0551</v>
+        <v>0.3637</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5889</v>
+        <v>-0.3219</v>
       </c>
       <c r="W22" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1111</v>
+        <v>-0.1766</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6604</v>
+        <v>0.372</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7715</v>
+        <v>-0.5485</v>
       </c>
       <c r="G23" t="n">
         <v>-0.3661</v>
@@ -2248,13 +2248,13 @@
         <v>0.5498</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6607</v>
+        <v>0.5952</v>
       </c>
       <c r="T23" t="n">
-        <v>1.1531</v>
+        <v>0.8646</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4924</v>
+        <v>-0.2694</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9554</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>F. BLASCO MANZANO</t>
+          <t>S. CARRION BALLESTER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2991</v>
+        <v>-0.764</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8952</v>
+        <v>-2.9021</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4039</v>
+        <v>2.1381</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1687</v>
+        <v>-1.9489</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.2783</v>
+        <v>-4.0167</v>
       </c>
       <c r="I24" t="n">
-        <v>3.1097</v>
+        <v>2.0678</v>
       </c>
       <c r="J24" t="n">
-        <v>1.8342</v>
+        <v>-1.735</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8269</v>
+        <v>-2.5208</v>
       </c>
       <c r="L24" t="n">
-        <v>2.6611</v>
+        <v>0.7857</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.0029</v>
+        <v>-0.2139</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.4514</v>
+        <v>-1.4959</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4486</v>
+        <v>1.2821</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.733</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.7489</v>
+        <v>-3.6651</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0158</v>
+        <v>2.3823</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0413</v>
+        <v>0.8788</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6244</v>
+        <v>0.9092</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4169</v>
+        <v>-0.0304</v>
       </c>
       <c r="V24" t="n">
-        <v>0.6439</v>
+        <v>1.5889</v>
       </c>
       <c r="W24" t="n">
-        <v>0.6439</v>
+        <v>1.5889</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.5961</v>
+        <v>-3.5306</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.8455</v>
+        <v>-1.557</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.7506</v>
+        <v>-1.9736</v>
       </c>
       <c r="G25" t="n">
         <v>-1.5296</v>
@@ -2404,13 +2404,13 @@
         <v>1.0995</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3493</v>
+        <v>-0.2838</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5324</v>
+        <v>-0.244</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1832</v>
+        <v>-0.0398</v>
       </c>
       <c r="V25" t="n">
         <v>-1.9005</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.7218</v>
+        <v>-3.5542</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.8355</v>
+        <v>-1.6432</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.8862</v>
+        <v>-1.911</v>
       </c>
       <c r="G26" t="n">
         <v>-2.0166</v>
@@ -2482,13 +2482,13 @@
         <v>1.6493</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0566</v>
+        <v>0.2242</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1637</v>
+        <v>0.356</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.107</v>
+        <v>-0.1318</v>
       </c>
       <c r="V26" t="n">
         <v>-1.5785</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-5.0854</v>
+        <v>-4.8713</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.9097</v>
+        <v>-3.6213</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.1757</v>
+        <v>-1.25</v>
       </c>
       <c r="G28" t="n">
         <v>-2.5909</v>
@@ -2638,13 +2638,13 @@
         <v>1.0995</v>
       </c>
       <c r="S28" t="n">
-        <v>0.6654</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="T28" t="n">
-        <v>0.0905</v>
+        <v>0.379</v>
       </c>
       <c r="U28" t="n">
-        <v>0.5749</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="V28" t="n">
         <v>0.3219</v>
@@ -2674,10 +2674,10 @@
         <v>-10.622</v>
       </c>
       <c r="E29" t="n">
-        <v>-8.2639</v>
+        <v>-8.2638</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.3581</v>
+        <v>-2.358099999999999</v>
       </c>
       <c r="G29" t="n">
         <v>-14.3703</v>
@@ -2689,10 +2689,10 @@
         <v>2.7247</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4688999999999993</v>
+        <v>0.4689</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.937399999999999</v>
+        <v>-1.9374</v>
       </c>
       <c r="L29" t="n">
         <v>2.406299999999999</v>
@@ -2716,16 +2716,16 @@
         <v>17.4092</v>
       </c>
       <c r="S29" t="n">
-        <v>6.319700000000001</v>
+        <v>6.3197</v>
       </c>
       <c r="T29" t="n">
-        <v>5.203799999999999</v>
+        <v>5.203899999999999</v>
       </c>
       <c r="U29" t="n">
-        <v>1.1161</v>
+        <v>1.1159</v>
       </c>
       <c r="V29" t="n">
-        <v>3.842500000000001</v>
+        <v>3.8425</v>
       </c>
       <c r="W29" t="n">
         <v>9.886499999999998</v>
